--- a/TeamsUsersImport.xlsx
+++ b/TeamsUsersImport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29629"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eric Marsi\Downloads\MSTeams\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\OH1-Fp1\Files\Personal Files\PC Mapping\To Do\Scripting\TeamsToolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3A4E0B-B977-47A2-87B5-24BF041F5498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9738AD56-769A-4AE2-BAA3-1B90E66C1D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14660" xr2:uid="{E669ADDA-0CC2-497C-9126-E11F26B94A20}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E669ADDA-0CC2-497C-9126-E11F26B94A20}"/>
   </bookViews>
   <sheets>
     <sheet name="TeamsUsersImport_v2408.2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>UserPrincipalName</t>
   </si>
@@ -47,9 +47,6 @@
     <t>LocationID</t>
   </si>
   <si>
-    <t>DirectRouting</t>
-  </si>
-  <si>
     <t>CsCallingLineIdentity</t>
   </si>
   <si>
@@ -95,13 +92,28 @@
     <t>CsTeamsSurvivableBranchAppliancePolicy</t>
   </si>
   <si>
-    <t>User@Domain.com</t>
-  </si>
-  <si>
-    <t>+13305550001</t>
-  </si>
-  <si>
-    <t>+13305550002</t>
+    <t>CsTeamsComplianceRecordingPolicy</t>
+  </si>
+  <si>
+    <t>CsTeamsVideoInteropServicePolicy</t>
+  </si>
+  <si>
+    <t>LicenseSKUsToAdd</t>
+  </si>
+  <si>
+    <t>peppa.pig@msftnet.co</t>
+  </si>
+  <si>
+    <t>LicenseSKUsToRemove</t>
+  </si>
+  <si>
+    <t>Blahhh, Microsoft_Teams_Rooms_Pro, BLAH</t>
+  </si>
+  <si>
+    <t>Blah, MCOMEETADV,FLOW_FREE, Microsoft_Teams_Rooms_Pro, Blah</t>
+  </si>
+  <si>
+    <t>PWExpires</t>
   </si>
 </sst>
 </file>
@@ -665,10 +677,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8339E755-B27D-4BAC-8424-FCE5C2023464}" name="Table1" displayName="Table1" ref="A1:S243" totalsRowShown="0">
-  <autoFilter ref="A1:S243" xr:uid="{8339E755-B27D-4BAC-8424-FCE5C2023464}"/>
-  <tableColumns count="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8339E755-B27D-4BAC-8424-FCE5C2023464}" name="Table1" displayName="Table1" ref="A1:X243" totalsRowShown="0">
+  <autoFilter ref="A1:X243" xr:uid="{8339E755-B27D-4BAC-8424-FCE5C2023464}"/>
+  <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{9AD3279C-7B5E-49E0-A45B-FAA52601FE8B}" name="UserPrincipalName"/>
+    <tableColumn id="22" xr3:uid="{6D021D08-BE92-42A9-B11D-A2249DA51959}" name="PWExpires" dataCellStyle="Normal"/>
+    <tableColumn id="23" xr3:uid="{A2193818-9A0F-4AC7-AB68-AABBC0612B0B}" name="LicenseSKUsToAdd"/>
+    <tableColumn id="24" xr3:uid="{58C891E6-7B83-4503-A15E-A4497C949E83}" name="LicenseSKUsToRemove"/>
     <tableColumn id="2" xr3:uid="{410EFA04-79F7-4B48-A2CD-9327F292D50F}" name="PhoneNumber" dataDxfId="1"/>
     <tableColumn id="19" xr3:uid="{609FDAEA-345C-41CD-B574-AEF981350D87}" name="PrivateLineNumber" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{DE2C16D0-6646-49BB-BCBA-E5B0342FB954}" name="PhoneNumberType"/>
@@ -680,11 +695,13 @@
     <tableColumn id="8" xr3:uid="{920AEBB6-D069-4F56-B5FF-8811865C5827}" name="CsOnlineVoiceRoutingPolicy"/>
     <tableColumn id="9" xr3:uid="{C44B1309-B882-4DA7-A8A8-132BECBC907A}" name="CsTeamsCallingPolicy"/>
     <tableColumn id="10" xr3:uid="{23294FDF-8FDB-4D79-8430-C97B7DE505DB}" name="CsTeamsCallParkPolicy"/>
+    <tableColumn id="18" xr3:uid="{AA97A447-BC2A-45EF-9376-5BCA3F2533F0}" name="CsTeamsComplianceRecordingPolicy"/>
     <tableColumn id="11" xr3:uid="{369EAC1E-0C47-4BD0-92B0-88071CE8658E}" name="CsTeamsEmergencyCallingPolicy"/>
     <tableColumn id="12" xr3:uid="{4C015EAD-B155-488A-88F4-24056F9255E0}" name="CsTeamsEmergencyCallRoutingPolicy"/>
     <tableColumn id="16" xr3:uid="{38C1C5FE-AF68-427A-9E0B-81F835C32CDB}" name="CsTeamsIPPhonePolicy"/>
     <tableColumn id="13" xr3:uid="{F767753C-5DD9-406F-A2AB-E12B6F3F58E6}" name="CsTeamsSharedCallingRoutingPolicy"/>
     <tableColumn id="20" xr3:uid="{99EC1374-5C60-4D47-BBBC-7F79B2D747A4}" name="CsTeamsSurvivableBranchAppliancePolicy"/>
+    <tableColumn id="21" xr3:uid="{723FD21C-3DC6-444F-8F77-6BCE50BD6BA3}" name="CsTeamsVideoInteropServicePolicy"/>
     <tableColumn id="14" xr3:uid="{17DFE96B-4A4D-4DD8-AA17-B325C3526F64}" name="CsTeamsVoiceApplicationsPolicy"/>
     <tableColumn id="15" xr3:uid="{413BD524-B48E-4443-9FBA-2A4CFAE43255}" name="CsTenantDialPlan"/>
   </tableColumns>
@@ -1009,103 +1026,123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0053EED3-24F3-481A-8987-00FC7A7950C1}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.453125" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.453125" customWidth="1"/>
-    <col min="5" max="5" width="34.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="34" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="38.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="39.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="8" max="8" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="V1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="X1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="B2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
       <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="b">
+        <v>24</v>
+      </c>
+      <c r="I2" t="b">
         <v>1</v>
       </c>
     </row>

--- a/TeamsUsersImport.xlsx
+++ b/TeamsUsersImport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\OH1-Fp1\Files\Personal Files\PC Mapping\To Do\Scripting\TeamsToolbox\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\OH1-Fp1\Files\Personal Files\PC Mapping\To Do\Scripting\TeamsToolbox\Release\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9738AD56-769A-4AE2-BAA3-1B90E66C1D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A458F3-01D6-4EEF-9824-BB0F42AC89B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E669ADDA-0CC2-497C-9126-E11F26B94A20}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E669ADDA-0CC2-497C-9126-E11F26B94A20}"/>
   </bookViews>
   <sheets>
     <sheet name="TeamsUsersImport_v2408.2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>UserPrincipalName</t>
   </si>
@@ -101,19 +101,28 @@
     <t>LicenseSKUsToAdd</t>
   </si>
   <si>
-    <t>peppa.pig@msftnet.co</t>
-  </si>
-  <si>
     <t>LicenseSKUsToRemove</t>
   </si>
   <si>
-    <t>Blahhh, Microsoft_Teams_Rooms_Pro, BLAH</t>
-  </si>
-  <si>
-    <t>Blah, MCOMEETADV,FLOW_FREE, Microsoft_Teams_Rooms_Pro, Blah</t>
-  </si>
-  <si>
     <t>PWExpires</t>
+  </si>
+  <si>
+    <t>user@domain.com</t>
+  </si>
+  <si>
+    <t>MCOEV</t>
+  </si>
+  <si>
+    <t>MCOEV, Microsoft_Teams_Rooms_Pro</t>
+  </si>
+  <si>
+    <t>+13305550001</t>
+  </si>
+  <si>
+    <t>+13305550002</t>
+  </si>
+  <si>
+    <t>DirectRouting</t>
   </si>
 </sst>
 </file>
@@ -1029,10 +1038,10 @@
   <dimension ref="A1:X2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.42578125" customWidth="1"/>
@@ -1060,13 +1069,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
         <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -1131,16 +1140,25 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" t="b">
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
-        <v>24</v>
+      <c r="E2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>29</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>

--- a/TeamsUsersImport.xlsx
+++ b/TeamsUsersImport.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29630"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\OH1-Fp1\Files\Personal Files\PC Mapping\To Do\Scripting\TeamsToolbox\Release\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\OH1-Fp1\Files\Personal Files\PC Mapping\To Do\Scripting\TeamsToolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A458F3-01D6-4EEF-9824-BB0F42AC89B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A9F590-4581-4004-A567-9A48573FA6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E669ADDA-0CC2-497C-9126-E11F26B94A20}"/>
   </bookViews>
   <sheets>
-    <sheet name="TeamsUsersImport_v2408.2" sheetId="1" r:id="rId1"/>
+    <sheet name="TeamsUsersImport_v2601.1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/TeamsUsersImport.xlsx
+++ b/TeamsUsersImport.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29630"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\OH1-Fp1\Files\Personal Files\PC Mapping\To Do\Scripting\TeamsToolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A9F590-4581-4004-A567-9A48573FA6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCAC88A-186D-479A-BE85-53159BE52478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E669ADDA-0CC2-497C-9126-E11F26B94A20}"/>
   </bookViews>
@@ -38,12 +38,6 @@
     <t>UserPrincipalName</t>
   </si>
   <si>
-    <t>PhoneNumber</t>
-  </si>
-  <si>
-    <t>PhoneNumberType</t>
-  </si>
-  <si>
     <t>LocationID</t>
   </si>
   <si>
@@ -123,6 +117,12 @@
   </si>
   <si>
     <t>DirectRouting</t>
+  </si>
+  <si>
+    <t>TelephoneNumber</t>
+  </si>
+  <si>
+    <t>NumberType</t>
   </si>
 </sst>
 </file>
@@ -273,7 +273,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -451,6 +451,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -615,10 +621,11 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -693,9 +700,9 @@
     <tableColumn id="22" xr3:uid="{6D021D08-BE92-42A9-B11D-A2249DA51959}" name="PWExpires" dataCellStyle="Normal"/>
     <tableColumn id="23" xr3:uid="{A2193818-9A0F-4AC7-AB68-AABBC0612B0B}" name="LicenseSKUsToAdd"/>
     <tableColumn id="24" xr3:uid="{58C891E6-7B83-4503-A15E-A4497C949E83}" name="LicenseSKUsToRemove"/>
-    <tableColumn id="2" xr3:uid="{410EFA04-79F7-4B48-A2CD-9327F292D50F}" name="PhoneNumber" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{410EFA04-79F7-4B48-A2CD-9327F292D50F}" name="TelephoneNumber" dataDxfId="1"/>
     <tableColumn id="19" xr3:uid="{609FDAEA-345C-41CD-B574-AEF981350D87}" name="PrivateLineNumber" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{DE2C16D0-6646-49BB-BCBA-E5B0342FB954}" name="PhoneNumberType"/>
+    <tableColumn id="3" xr3:uid="{DE2C16D0-6646-49BB-BCBA-E5B0342FB954}" name="NumberType"/>
     <tableColumn id="4" xr3:uid="{C5C71BC0-25DD-4D8B-AA97-833F492556C9}" name="LocationID"/>
     <tableColumn id="17" xr3:uid="{D267C159-95CE-48A8-96E9-B0DCBF1F1B18}" name="EnterpriseVoiceEnabled"/>
     <tableColumn id="5" xr3:uid="{7B8DDE5F-5719-4D68-863E-9C187F274C23}" name="CsCallingLineIdentity"/>
@@ -1040,11 +1047,11 @@
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.140625" bestFit="1" customWidth="1"/>
@@ -1069,96 +1076,96 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="Q1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="S1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="U1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="V1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>6</v>
-      </c>
-      <c r="R1" t="s">
+      <c r="X1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="S1" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" t="s">
-        <v>13</v>
-      </c>
-      <c r="X1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="b">
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" t="s">
         <v>27</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>29</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
